--- a/archive/InnovateUK_Funding_Opportunities_WeeklyBreakdown_2026-03-12.xlsx
+++ b/archive/InnovateUK_Funding_Opportunities_WeeklyBreakdown_2026-03-12.xlsx
@@ -487,10 +487,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -9171,7 +9171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9254,26 +9254,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/clean-maritime-demonstration-competition-7/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-12 10:27</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46092.44027777778</v>
+        <v>46093.43541666667</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -9282,11 +9282,17 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>46092</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>15/07/2026                              11:00</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -9294,7 +9300,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£121.0 million</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
@@ -9312,12 +9318,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -9347,7 +9353,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N3" s="2" t="n">
@@ -9365,12 +9371,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -9400,13 +9406,66 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£15.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="O4" s="1" t="n">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-11 10:34</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46092.44027777778</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Wednesday 15 July 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>46218.45833333334</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>£15.0 million</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>46092</v>
       </c>
     </row>
